--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_40.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_40.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IVCat</t>
+          <t>ReactionTime</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>Diligence</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-1.204472157610847</v>
+        <v>-1.349564459763454</v>
       </c>
       <c r="C2">
-        <v>-0.826906072177134</v>
+        <v>-1.008742514975132</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.218452774698904</v>
+        <v>0.4167410773491825</v>
       </c>
       <c r="C3">
-        <v>0.2053197422062383</v>
+        <v>0.02136586463824289</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.8346283049488129</v>
+        <v>-0.8141322654444736</v>
       </c>
       <c r="C4">
-        <v>0.2968602067620136</v>
+        <v>2.037788832280906</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.06478196506697631</v>
+        <v>1.144516477497953</v>
       </c>
       <c r="C5">
-        <v>-0.3876034579299393</v>
+        <v>1.037385682626674</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.4966266740070979</v>
+        <v>0.3511099387471223</v>
       </c>
       <c r="C6">
-        <v>0.647663324505892</v>
+        <v>-0.1349985787626375</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.8257587043573454</v>
+        <v>0.276803047067357</v>
       </c>
       <c r="C7">
-        <v>0.9508107947034314</v>
+        <v>0.5456693427031759</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8610459737523368</v>
+        <v>2.204373697475513</v>
       </c>
       <c r="C8">
-        <v>-0.8460575354479808</v>
+        <v>0.5772572362462509</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.108533813456061</v>
+        <v>-1.323074312314793</v>
       </c>
       <c r="C9">
-        <v>0.6093945266434668</v>
+        <v>-0.2169515358966062</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-1.923732946985059</v>
+        <v>-0.7167086898782236</v>
       </c>
       <c r="C10">
-        <v>0.5919114237088896</v>
+        <v>-1.678706854335778</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.5533372677624427</v>
+        <v>-0.1256068850866257</v>
       </c>
       <c r="C11">
-        <v>-0.2299782971341931</v>
+        <v>-0.2859036828873489</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.7412250750334636</v>
+        <v>0.8406830937399336</v>
       </c>
       <c r="C12">
-        <v>1.095216073361965</v>
+        <v>0.780485127337734</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-2.191752962661655</v>
+        <v>1.241077837127717</v>
       </c>
       <c r="C13">
-        <v>1.938221434338494</v>
+        <v>1.386647703223103</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.406288985338938</v>
+        <v>-1.673023811135514</v>
       </c>
       <c r="C14">
-        <v>-0.4727556612880069</v>
+        <v>-1.460487539578227</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>2.55218333648994</v>
+        <v>-1.438525635316284</v>
       </c>
       <c r="C15">
-        <v>0.293216651756979</v>
+        <v>-1.362989144815129</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9979470407900799</v>
+        <v>-0.4712068284521012</v>
       </c>
       <c r="C16">
-        <v>-1.653685522182941</v>
+        <v>-0.2891442134233825</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.2589466572213293</v>
+        <v>-1.209721319324595</v>
       </c>
       <c r="C17">
-        <v>0.842930840128356</v>
+        <v>0.3830607138853919</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.5271615313967817</v>
+        <v>-0.6805815458740359</v>
       </c>
       <c r="C18">
-        <v>-1.795654828128053</v>
+        <v>-1.186668700012289</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.269161169243062</v>
+        <v>-0.4194708932128001</v>
       </c>
       <c r="C19">
-        <v>0.6339958401083743</v>
+        <v>-1.741493056853292</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>2.037394314114593</v>
+        <v>-1.027395512396897</v>
       </c>
       <c r="C20">
-        <v>0.8880956295275244</v>
+        <v>-0.8901459476091897</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>2.428489579209621</v>
+        <v>0.02691868817064159</v>
       </c>
       <c r="C21">
-        <v>-0.6632337009050384</v>
+        <v>0.8091884634335145</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.06677627990817865</v>
+        <v>0.3744251610932063</v>
       </c>
       <c r="C22">
-        <v>-1.709026319732212</v>
+        <v>-0.1227698416365104</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.4104745533818642</v>
+        <v>1.336686174156738</v>
       </c>
       <c r="C23">
-        <v>-1.256786877157804</v>
+        <v>0.8407053255495256</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.221570752664046</v>
+        <v>1.663185981505012</v>
       </c>
       <c r="C24">
-        <v>-1.416651689016935</v>
+        <v>2.031310349815021</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.3777031487141327</v>
+        <v>0.7097687312277224</v>
       </c>
       <c r="C25">
-        <v>0.9472160188679777</v>
+        <v>0.1925040410697365</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.6476007462463413</v>
+        <v>0.1448810280419081</v>
       </c>
       <c r="C26">
-        <v>-0.5797107595266566</v>
+        <v>-0.3280190244441894</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>2.031337227380874</v>
+        <v>-0.4648266324619753</v>
       </c>
       <c r="C27">
-        <v>-0.837643051411449</v>
+        <v>-0.5695383603573159</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.8977885342639987</v>
+        <v>0.4023399505707431</v>
       </c>
       <c r="C28">
-        <v>-0.3008499951742305</v>
+        <v>-1.454820188313744</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.8438028478524863</v>
+        <v>0.04027944668142168</v>
       </c>
       <c r="C29">
-        <v>-0.544914833834268</v>
+        <v>-0.580062880873133</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.5846904202026372</v>
+        <v>-0.4857419111548232</v>
       </c>
       <c r="C30">
-        <v>0.1500365847513404</v>
+        <v>0.5638549883940638</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.407485539174639</v>
+        <v>0.2799743965511429</v>
       </c>
       <c r="C31">
-        <v>-1.329194122225438</v>
+        <v>-0.04464878822422405</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.00994593179276528</v>
+        <v>0.9809157621730881</v>
       </c>
       <c r="C32">
-        <v>-0.1329354602055315</v>
+        <v>0.3505588491380379</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.5734936673160039</v>
+        <v>-1.405431997109957</v>
       </c>
       <c r="C33">
-        <v>-0.7589401795340994</v>
+        <v>-0.5215855088950033</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.5391686772243782</v>
+        <v>-0.3636346820965451</v>
       </c>
       <c r="C34">
-        <v>0.2745974374828597</v>
+        <v>0.6172717549183016</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.3735266518765751</v>
+        <v>0.5944933900985645</v>
       </c>
       <c r="C35">
-        <v>-1.278229318089686</v>
+        <v>0.3734869600540425</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.704313499343703</v>
+        <v>-0.4616744896309218</v>
       </c>
       <c r="C36">
-        <v>1.18592660717788</v>
+        <v>-0.7713630031694854</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.19824017365725</v>
+        <v>0.5676644935109848</v>
       </c>
       <c r="C37">
-        <v>0.6047077600150061</v>
+        <v>0.1080278002612153</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.5548610830594379</v>
+        <v>-0.08694053647215955</v>
       </c>
       <c r="C38">
-        <v>-1.136700729688721</v>
+        <v>-1.347885601862041</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.4630423808075734</v>
+        <v>-0.4504399487635994</v>
       </c>
       <c r="C39">
-        <v>-1.726784600885841</v>
+        <v>-1.301956704661549</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.583127516378345</v>
+        <v>3.263203327848012</v>
       </c>
       <c r="C40">
-        <v>-0.162008665248</v>
+        <v>2.007282819965102</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.5541310660551536</v>
+        <v>-1.264703875511066</v>
       </c>
       <c r="C41">
-        <v>-0.8986224403645224</v>
+        <v>-0.3888464449079848</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.2931619905378802</v>
+        <v>-0.05405698606712235</v>
       </c>
       <c r="C42">
-        <v>0.9553542329486904</v>
+        <v>-0.1331407785282109</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.9301521684722938</v>
+        <v>-0.007750478703181707</v>
       </c>
       <c r="C43">
-        <v>1.282792884375637</v>
+        <v>2.082571438857998</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.678151737450952</v>
+        <v>-0.2253687005861458</v>
       </c>
       <c r="C44">
-        <v>0.675364465930149</v>
+        <v>0.5452252380253717</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.2806428347998584</v>
+        <v>0.8649798838884563</v>
       </c>
       <c r="C45">
-        <v>1.814725110040459</v>
+        <v>1.13231421955141</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.221862527321876</v>
+        <v>-0.01814384112899263</v>
       </c>
       <c r="C46">
-        <v>0.3154482915424172</v>
+        <v>-0.2976613964280712</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.1314468530871747</v>
+        <v>-1.584309435486786</v>
       </c>
       <c r="C47">
-        <v>1.717429349828956</v>
+        <v>-1.774621473775668</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.9576256623406757</v>
+        <v>-0.09396131390548883</v>
       </c>
       <c r="C48">
-        <v>-0.7828769079744802</v>
+        <v>-0.02286109416883728</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.8309717192630627</v>
+        <v>-1.393374760818165</v>
       </c>
       <c r="C49">
-        <v>1.563709479617363</v>
+        <v>0.06573256606584632</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.3738065328207816</v>
+        <v>-1.001999109674655</v>
       </c>
       <c r="C50">
-        <v>0.3649170835417819</v>
+        <v>-2.636900650626625</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.3531535257569453</v>
+        <v>1.087329649083463</v>
       </c>
       <c r="C51">
-        <v>0.3871819758301908</v>
+        <v>0.03713867253034836</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>0.8129627083799202</v>
+        <v>-0.3454253154216274</v>
       </c>
       <c r="C52">
-        <v>-0.3476312618316553</v>
+        <v>-0.858733839741576</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.4786529482654865</v>
+        <v>1.223065852927599</v>
       </c>
       <c r="C53">
-        <v>0.502033633128505</v>
+        <v>-0.02128214632975106</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.4383450457903067</v>
+        <v>-0.5972083778137054</v>
       </c>
       <c r="C54">
-        <v>1.280302483785246</v>
+        <v>1.174739956136097</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.7247375968632691</v>
+        <v>-0.4130775150635347</v>
       </c>
       <c r="C55">
-        <v>0.4494796279820408</v>
+        <v>-0.2464020822656869</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-1.760379964147826</v>
+        <v>-0.9459917723177413</v>
       </c>
       <c r="C56">
-        <v>0.1156059504739845</v>
+        <v>-1.245463520807958</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.3274100785935624</v>
+        <v>0.9086019834094247</v>
       </c>
       <c r="C57">
-        <v>0.7103207631744262</v>
+        <v>0.1740468232249441</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.4192078612170247</v>
+        <v>-0.8816351560891786</v>
       </c>
       <c r="C58">
-        <v>-0.8638837757484792</v>
+        <v>-1.32032990380973</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.2356561084025957</v>
+        <v>-0.4328462506860959</v>
       </c>
       <c r="C59">
-        <v>0.01528280809776938</v>
+        <v>-0.0774026868370175</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.0709293999609943</v>
+        <v>0.5033484895467938</v>
       </c>
       <c r="C60">
-        <v>-1.103813020175072</v>
+        <v>-0.03070152882813332</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.5577789844674815</v>
+        <v>-1.71525419696952</v>
       </c>
       <c r="C61">
-        <v>-0.6967567803041819</v>
+        <v>0.1627607482289594</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.05384265522908963</v>
+        <v>1.375960373520602</v>
       </c>
       <c r="C62">
-        <v>-1.261090605325044</v>
+        <v>0.3180751213364861</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.7774370589611079</v>
+        <v>0.6173451770678591</v>
       </c>
       <c r="C63">
-        <v>-0.3323582363584726</v>
+        <v>-1.127050522301896</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>-1.163450228512124</v>
+        <v>1.872579072270403</v>
       </c>
       <c r="C64">
-        <v>1.112051345111692</v>
+        <v>0.5482331808216466</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.690379353105628</v>
+        <v>-0.7852335689548435</v>
       </c>
       <c r="C65">
-        <v>-1.370954705921608</v>
+        <v>0.5369486079883106</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>1.500752724264493</v>
+        <v>0.6780819830468364</v>
       </c>
       <c r="C66">
-        <v>-0.2136256089783848</v>
+        <v>0.6895992097162437</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-1.400624438706193</v>
+        <v>1.190491619684813</v>
       </c>
       <c r="C67">
-        <v>-0.03831420802579311</v>
+        <v>1.397300543949681</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-1.481210075915032</v>
+        <v>0.4401165589288773</v>
       </c>
       <c r="C68">
-        <v>0.2211144886524084</v>
+        <v>1.008900798376335</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.4826959167344986</v>
+        <v>0.2652669701796358</v>
       </c>
       <c r="C69">
-        <v>0.1326211678508021</v>
+        <v>0.1661739422610809</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.2840870852698292</v>
+        <v>-0.1584343289588032</v>
       </c>
       <c r="C70">
-        <v>-0.5150664541735381</v>
+        <v>-1.533164422339833</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.8819552562381596</v>
+        <v>-0.2485995846426382</v>
       </c>
       <c r="C71">
-        <v>-1.898361592231913</v>
+        <v>-0.128289418837948</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-0.2859570312493497</v>
+        <v>1.411077980135559</v>
       </c>
       <c r="C72">
-        <v>-1.345494625362391</v>
+        <v>0.1724903827298842</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-1.490552814487766</v>
+        <v>-0.372664338081348</v>
       </c>
       <c r="C73">
-        <v>-1.329616636115627</v>
+        <v>-0.2126586013183113</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.7011826129468677</v>
+        <v>1.231398726377648</v>
       </c>
       <c r="C74">
-        <v>0.8930052291730808</v>
+        <v>0.3794822437965282</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.7361808426086255</v>
+        <v>2.7053000565953</v>
       </c>
       <c r="C75">
-        <v>-1.584153849668538</v>
+        <v>-0.8402912518469554</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.3950822913382649</v>
+        <v>-0.5324186609989977</v>
       </c>
       <c r="C76">
-        <v>0.143815637321422</v>
+        <v>-0.09643967870454012</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-0.2586402010067562</v>
+        <v>-0.5728814652634455</v>
       </c>
       <c r="C77">
-        <v>-0.4403317425111881</v>
+        <v>-0.7081663816036406</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.6461678519375794</v>
+        <v>1.096894489181133</v>
       </c>
       <c r="C78">
-        <v>-0.1410481588088522</v>
+        <v>-0.104210495855825</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.09417003665926976</v>
+        <v>-0.5289484479666804</v>
       </c>
       <c r="C79">
-        <v>-0.7046651258035569</v>
+        <v>0.2800119950969281</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.6185613621037972</v>
+        <v>0.6324119494536212</v>
       </c>
       <c r="C80">
-        <v>-0.7794736868704701</v>
+        <v>0.7357333658487337</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-1.076892698879757</v>
+        <v>-0.3399085855370861</v>
       </c>
       <c r="C81">
-        <v>-0.008388477241103032</v>
+        <v>-0.03251049975981478</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.1622746769734801</v>
+        <v>-0.8535817825899159</v>
       </c>
       <c r="C82">
-        <v>-0.957535109414734</v>
+        <v>-0.5356209426415908</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>0.9136338671235831</v>
+        <v>0.8254968120820035</v>
       </c>
       <c r="C83">
-        <v>-1.674796666812805</v>
+        <v>-0.3584370490609211</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-1.119323376818343</v>
+        <v>0.2756363269092659</v>
       </c>
       <c r="C84">
-        <v>-0.134558596101046</v>
+        <v>0.3362810867126562</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-1.535587880596785</v>
+        <v>0.02987585128956145</v>
       </c>
       <c r="C85">
-        <v>-0.4933011923008379</v>
+        <v>-0.7743321520985031</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>1.101526510482726</v>
+        <v>2.202703436941576</v>
       </c>
       <c r="C86">
-        <v>-0.2629008502262709</v>
+        <v>1.09571567492964</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.003771474033743566</v>
+        <v>-0.4747305706342733</v>
       </c>
       <c r="C87">
-        <v>0.2843511294441055</v>
+        <v>-0.6907048080221246</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-1.735508091318321</v>
+        <v>-0.1855938425153901</v>
       </c>
       <c r="C88">
-        <v>-0.7704022581855675</v>
+        <v>-0.3228966342744548</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.6703567992183569</v>
+        <v>0.6183166284383881</v>
       </c>
       <c r="C89">
-        <v>-1.342961350704375</v>
+        <v>-0.6425844061316113</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>2.096390422552493</v>
+        <v>-1.062585599234198</v>
       </c>
       <c r="C90">
-        <v>-0.6534729968755749</v>
+        <v>0.6585491692049337</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>0.09900431340242627</v>
+        <v>0.8736701132615415</v>
       </c>
       <c r="C91">
-        <v>-0.6461982860508981</v>
+        <v>-0.259003422894125</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-0.54690815503339</v>
+        <v>-1.352072426109671</v>
       </c>
       <c r="C92">
-        <v>-0.519580796213855</v>
+        <v>-2.134230022841176</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.9877254969969206</v>
+        <v>-0.7036088900177099</v>
       </c>
       <c r="C93">
-        <v>-0.4663503524190407</v>
+        <v>0.4893596049059343</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.6160326078633869</v>
+        <v>0.6077891152397156</v>
       </c>
       <c r="C94">
-        <v>0.4954060791887415</v>
+        <v>0.463891390678313</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.2267117716772268</v>
+        <v>-0.1221742919484348</v>
       </c>
       <c r="C95">
-        <v>-0.5718399714118837</v>
+        <v>-0.7635310137495857</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-1.338778872366839</v>
+        <v>-1.560462897012288</v>
       </c>
       <c r="C96">
-        <v>-0.3674826940319106</v>
+        <v>0.3193298569501264</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-1.233606647419749</v>
+        <v>-1.029885711389712</v>
       </c>
       <c r="C97">
-        <v>0.7603418105570203</v>
+        <v>-1.344697622613931</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>1.785493600734378</v>
+        <v>-0.5691359027250263</v>
       </c>
       <c r="C98">
-        <v>0.6183910602204505</v>
+        <v>-0.01821257738010976</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-0.6161549995684507</v>
+        <v>-1.979016265677923</v>
       </c>
       <c r="C99">
-        <v>-0.9556952469977003</v>
+        <v>0.3112233465440195</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.7800749811136523</v>
+        <v>-0.6578964515317038</v>
       </c>
       <c r="C100">
-        <v>-1.070750556553149</v>
+        <v>-0.6636066183122387</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.3568014226485873</v>
+        <v>1.853129213547263</v>
       </c>
       <c r="C101">
-        <v>0.8536509153070255</v>
+        <v>0.5420820138220481</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>-2.420062324485719</v>
+        <v>-1.799445272309943</v>
       </c>
       <c r="C102">
-        <v>0.7087531655771375</v>
+        <v>-0.01017157696575111</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>-1.338138266675452</v>
+        <v>-1.249370356846015</v>
       </c>
       <c r="C103">
-        <v>-0.2691679789540989</v>
+        <v>-0.6031080262815541</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>1.59802546128922</v>
+        <v>0.2208568714077921</v>
       </c>
       <c r="C104">
-        <v>-1.19506705822321</v>
+        <v>0.9743563940665771</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.09395160506888658</v>
+        <v>-0.6609957149434487</v>
       </c>
       <c r="C105">
-        <v>-0.3215422251914952</v>
+        <v>-0.337262059507878</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.351755418888937</v>
+        <v>-0.4518125548288907</v>
       </c>
       <c r="C106">
-        <v>-0.2033361413466464</v>
+        <v>-0.9819596132268401</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-1.406698930823729</v>
+        <v>-1.568035449111032</v>
       </c>
       <c r="C107">
-        <v>1.466678711295068</v>
+        <v>-2.03466080034549</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>0.3582285897382726</v>
+        <v>-2.075498412619991</v>
       </c>
       <c r="C108">
-        <v>-1.277336640224942</v>
+        <v>-0.9619061976250799</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>1.151538911393115</v>
+        <v>-0.05091944396834277</v>
       </c>
       <c r="C109">
-        <v>-0.1842907667296586</v>
+        <v>1.387874373231185</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.1501088416849887</v>
+        <v>0.4262249595132355</v>
       </c>
       <c r="C110">
-        <v>-1.191690183119775</v>
+        <v>1.240224380571466</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.3323091410608838</v>
+        <v>1.009059803591297</v>
       </c>
       <c r="C111">
-        <v>-1.181620300844274</v>
+        <v>-1.534519697129437</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.9292892374107486</v>
+        <v>1.245509307836236</v>
       </c>
       <c r="C112">
-        <v>0.4750918806367354</v>
+        <v>-0.3455617893129727</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>-1.394371830277842</v>
+        <v>-0.7832491306470978</v>
       </c>
       <c r="C113">
-        <v>-0.5348985177017087</v>
+        <v>-1.64084337051735</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>-0.1702949209758006</v>
+        <v>-0.5051688566057708</v>
       </c>
       <c r="C114">
-        <v>1.556197378551653</v>
+        <v>1.130360691953747</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>-0.07493547132556336</v>
+        <v>1.987903099182367</v>
       </c>
       <c r="C115">
-        <v>-1.169180578121932</v>
+        <v>-1.084207092109543</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.1879807348263837</v>
+        <v>-1.017502488165974</v>
       </c>
       <c r="C116">
-        <v>0.4340213383181162</v>
+        <v>1.152204947116975</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>-0.2334600892699068</v>
+        <v>-0.3032888880699772</v>
       </c>
       <c r="C117">
-        <v>-0.1237144315128464</v>
+        <v>-0.6768359754559656</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>-0.3749109782100302</v>
+        <v>0.8358920630994303</v>
       </c>
       <c r="C118">
-        <v>-0.009699317128306489</v>
+        <v>1.519363637993911</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.2347587262901743</v>
+        <v>-0.588237079125509</v>
       </c>
       <c r="C119">
-        <v>-0.2080218621955395</v>
+        <v>-0.2883999047033374</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.9275612916222957</v>
+        <v>-1.342761754538861</v>
       </c>
       <c r="C120">
-        <v>-1.384445980981768</v>
+        <v>-0.5203812222370326</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>-1.01441501770807</v>
+        <v>-1.037215261970253</v>
       </c>
       <c r="C121">
-        <v>0.2234303678869652</v>
+        <v>-0.1550079877417063</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-0.3104548264095522</v>
+        <v>-1.20377381829158</v>
       </c>
       <c r="C122">
-        <v>0.08531116516271557</v>
+        <v>1.267811657663586</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>-0.3048674678244091</v>
+        <v>0.5230733542543631</v>
       </c>
       <c r="C123">
-        <v>0.5559761443044877</v>
+        <v>0.03918335593047392</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.917686644140022</v>
+        <v>0.2301568707216153</v>
       </c>
       <c r="C124">
-        <v>-0.8122933874533304</v>
+        <v>0.3346979661609831</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.7700358747628423</v>
+        <v>-0.9343476839223753</v>
       </c>
       <c r="C125">
-        <v>0.7477930146169913</v>
+        <v>-0.04060392761765802</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-1.629192642812407</v>
+        <v>-0.7836889476995401</v>
       </c>
       <c r="C126">
-        <v>1.429333797128706</v>
+        <v>-0.7709823504323295</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>1.294527961239752</v>
+        <v>-0.5976519173893764</v>
       </c>
       <c r="C127">
-        <v>-0.5945349098412743</v>
+        <v>-1.184931446277542</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.673803121310589</v>
+        <v>0.4019017659821632</v>
       </c>
       <c r="C128">
-        <v>-0.3021512121139054</v>
+        <v>1.175022415848219</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>-2.433058045498901</v>
+        <v>0.9582201048531006</v>
       </c>
       <c r="C129">
-        <v>-0.1484046670671773</v>
+        <v>0.7508455445304101</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>-1.426160437694725</v>
+        <v>-1.205408073570905</v>
       </c>
       <c r="C130">
-        <v>1.856638176291535</v>
+        <v>-0.2653813189803547</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>-0.1140132074149889</v>
+        <v>1.042446275419223</v>
       </c>
       <c r="C131">
-        <v>0.8774342757646253</v>
+        <v>-0.8332750707771712</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>1.348473547168925</v>
+        <v>0.3870422075956426</v>
       </c>
       <c r="C132">
-        <v>-1.640956008136216</v>
+        <v>-0.2109708562363681</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>-0.9459338491844534</v>
+        <v>-0.3496487796271051</v>
       </c>
       <c r="C133">
-        <v>0.758711045220811</v>
+        <v>0.7472251943615387</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>1.174980375728903</v>
+        <v>1.632147800615032</v>
       </c>
       <c r="C134">
-        <v>0.3720432609685247</v>
+        <v>-0.6424073292226763</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>1.015856403245843</v>
+        <v>1.135066990969219</v>
       </c>
       <c r="C135">
-        <v>-1.076284086620209</v>
+        <v>0.06010983181501728</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>0.8526953809363201</v>
+        <v>-0.4156136188577375</v>
       </c>
       <c r="C136">
-        <v>0.4498542580746497</v>
+        <v>-0.5248725499771516</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>-0.8569579161223893</v>
+        <v>1.641463005393267</v>
       </c>
       <c r="C137">
-        <v>0.6494593424698842</v>
+        <v>1.190054671527625</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.6424031408187302</v>
+        <v>0.3050505870178502</v>
       </c>
       <c r="C138">
-        <v>-0.4191292028032198</v>
+        <v>0.9821387091408783</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>1.775034826120937</v>
+        <v>-0.9977437248676809</v>
       </c>
       <c r="C139">
-        <v>-1.222406919547673</v>
+        <v>-1.402541972241949</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>-1.29021522831468</v>
+        <v>-0.3718986091081148</v>
       </c>
       <c r="C140">
-        <v>1.511004895568248</v>
+        <v>-1.281707596927537</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.1534126924286319</v>
+        <v>0.9791545595195432</v>
       </c>
       <c r="C141">
-        <v>0.7996139207568014</v>
+        <v>0.4628170064651006</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-0.8074785943029087</v>
+        <v>-0.01704319244559363</v>
       </c>
       <c r="C142">
-        <v>-0.1976871089135261</v>
+        <v>0.5271569952706375</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>-0.5380872826184058</v>
+        <v>-0.4841484822610675</v>
       </c>
       <c r="C143">
-        <v>-0.516508901418393</v>
+        <v>-1.236109140364903</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.3261020171635274</v>
+        <v>-0.1074635495536211</v>
       </c>
       <c r="C144">
-        <v>0.1867461020168723</v>
+        <v>-0.4522300863008323</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>1.20782254314614</v>
+        <v>-1.045669306993288</v>
       </c>
       <c r="C145">
-        <v>-2.054862551508315</v>
+        <v>-0.1654571939831171</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>2.22573126751263</v>
+        <v>-1.289479617739251</v>
       </c>
       <c r="C146">
-        <v>-1.203383039091327</v>
+        <v>-0.09510577774334456</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>0.8570481109863425</v>
+        <v>0.8123045645722871</v>
       </c>
       <c r="C147">
-        <v>-0.9600736593930772</v>
+        <v>-0.2790869919232426</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>-0.5637604268505451</v>
+        <v>-0.8519921585838334</v>
       </c>
       <c r="C148">
-        <v>0.3278751401630641</v>
+        <v>0.1524089094159687</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-0.0234705681871473</v>
+        <v>1.488635098308376</v>
       </c>
       <c r="C149">
-        <v>-0.7977598568020232</v>
+        <v>1.867888507179437</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.5687898737216496</v>
+        <v>-0.2811482696457107</v>
       </c>
       <c r="C150">
-        <v>0.247821489205063</v>
+        <v>0.004662520275514809</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.7890025361763946</v>
+        <v>1.388108070434343</v>
       </c>
       <c r="C151">
-        <v>-2.152124155990123</v>
+        <v>-0.2941025112701563</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>0.971093947157605</v>
+        <v>0.3330984640677593</v>
       </c>
       <c r="C152">
-        <v>-0.6869341405947782</v>
+        <v>-0.5374635331148743</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-0.2532556880172402</v>
+        <v>-1.164856344986392</v>
       </c>
       <c r="C153">
-        <v>-0.6144553036836473</v>
+        <v>-1.368502736363893</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.3783908500924939</v>
+        <v>-0.06158943701148448</v>
       </c>
       <c r="C154">
-        <v>-1.586942220467156</v>
+        <v>1.13964578652714</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.8861010229832671</v>
+        <v>0.4420600449842931</v>
       </c>
       <c r="C155">
-        <v>0.4065824564946838</v>
+        <v>1.431652248210802</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.9772085674063089</v>
+        <v>2.385258770825883</v>
       </c>
       <c r="C156">
-        <v>-0.3053309192652857</v>
+        <v>1.450220622589708</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>-0.0148147263655459</v>
+        <v>0.9486137547012035</v>
       </c>
       <c r="C157">
-        <v>-1.3710531427008</v>
+        <v>0.05796523909339368</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>0.2010030390678494</v>
+        <v>0.4580426768782757</v>
       </c>
       <c r="C158">
-        <v>-1.210938643288918</v>
+        <v>-0.2538540063145614</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>0.7151452125467425</v>
+        <v>2.26909243173323</v>
       </c>
       <c r="C159">
-        <v>-0.1642124960206129</v>
+        <v>0.8461757687130181</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>0.5152078843257615</v>
+        <v>1.167823556808937</v>
       </c>
       <c r="C160">
-        <v>-0.5907910398111025</v>
+        <v>-0.4723771043591853</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>-0.01663553312128335</v>
+        <v>0.08930771499816038</v>
       </c>
       <c r="C161">
-        <v>0.3525865762755482</v>
+        <v>-0.06856986502965903</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>-0.5268895680682768</v>
+        <v>-2.512656292323336</v>
       </c>
       <c r="C162">
-        <v>2.210634795258787</v>
+        <v>-1.308019224429573</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>-0.945205190543939</v>
+        <v>-0.4286587571930777</v>
       </c>
       <c r="C163">
-        <v>-0.814353941348223</v>
+        <v>-0.09557902211915589</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.2611575395381001</v>
+        <v>-0.5943571564232528</v>
       </c>
       <c r="C164">
-        <v>-0.8418270132405132</v>
+        <v>-1.091683624300303</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>0.7392081124375547</v>
+        <v>-2.14216980928957</v>
       </c>
       <c r="C165">
-        <v>-0.1272326979969896</v>
+        <v>-1.6810904104313</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>1.006262605502622</v>
+        <v>2.367052301990068</v>
       </c>
       <c r="C166">
-        <v>0.3511187240900609</v>
+        <v>1.493798771428586</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-1.058870407923252</v>
+        <v>0.3050364446538464</v>
       </c>
       <c r="C167">
-        <v>-0.1016031416233557</v>
+        <v>0.2672986944915242</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>-0.7643678871194907</v>
+        <v>0.1452230429187005</v>
       </c>
       <c r="C168">
-        <v>-1.892669055769697</v>
+        <v>0.4437571993350397</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>-0.2590599400267569</v>
+        <v>1.994641895406591</v>
       </c>
       <c r="C169">
-        <v>-0.5362647201451143</v>
+        <v>-0.4581475622623972</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>-0.3708547492299665</v>
+        <v>-0.7959701847605966</v>
       </c>
       <c r="C170">
-        <v>0.8386258507302922</v>
+        <v>0.6680896422118536</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>0.7370904543576768</v>
+        <v>-0.3442391056594045</v>
       </c>
       <c r="C171">
-        <v>-0.9388217889152861</v>
+        <v>0.833405257086054</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>1.004419057554378</v>
+        <v>-0.3343195514517389</v>
       </c>
       <c r="C172">
-        <v>1.150109649101476</v>
+        <v>0.2060198743274412</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>0.1639043513803472</v>
+        <v>-0.01394051795725535</v>
       </c>
       <c r="C173">
-        <v>0.4508637817728661</v>
+        <v>0.7193051124239774</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.010570755571073</v>
+        <v>-0.3975127886491557</v>
       </c>
       <c r="C174">
-        <v>0.2989821874323441</v>
+        <v>0.1415390966638566</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>-0.2990695744144005</v>
+        <v>0.9110889359435863</v>
       </c>
       <c r="C175">
-        <v>0.4163328351169788</v>
+        <v>0.4359164973774403</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>-0.6484918318598651</v>
+        <v>0.08646462525951745</v>
       </c>
       <c r="C176">
-        <v>0.5060579928689397</v>
+        <v>0.8080267423748529</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-0.1377412533130542</v>
+        <v>2.244480429679445</v>
       </c>
       <c r="C177">
-        <v>0.5449654719913395</v>
+        <v>0.06130697744713254</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>-0.2738230721809997</v>
+        <v>-0.7161535173019465</v>
       </c>
       <c r="C178">
-        <v>0.7510227814751925</v>
+        <v>-0.7009175539461228</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-1.466162020664244</v>
+        <v>1.436859497708512</v>
       </c>
       <c r="C179">
-        <v>0.3726907377329034</v>
+        <v>1.104523461431</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>-0.6810326934187457</v>
+        <v>0.4096408298460679</v>
       </c>
       <c r="C180">
-        <v>0.4913026254909671</v>
+        <v>-1.898215310421768</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>-1.335039813300697</v>
+        <v>1.351091388321082</v>
       </c>
       <c r="C181">
-        <v>0.4783755672350479</v>
+        <v>0.3070223347327025</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.1933385345680701</v>
+        <v>0.7479569862561032</v>
       </c>
       <c r="C182">
-        <v>-0.5033328372957693</v>
+        <v>0.8218696221338913</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>0.212002233664092</v>
+        <v>1.025403885460685</v>
       </c>
       <c r="C183">
-        <v>0.345435219675741</v>
+        <v>1.197844719770732</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>-1.316262248834025</v>
+        <v>1.061634188910027</v>
       </c>
       <c r="C184">
-        <v>-0.03280341804465281</v>
+        <v>0.154735741274708</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>-0.2129542514241697</v>
+        <v>-0.4234625989182066</v>
       </c>
       <c r="C185">
-        <v>-0.7798782601884319</v>
+        <v>0.8456639803968975</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>0.1981687995227327</v>
+        <v>1.875617901940005</v>
       </c>
       <c r="C186">
-        <v>-0.07727238497217306</v>
+        <v>0.3670423255857166</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.7417589285179251</v>
+        <v>0.04695808298149561</v>
       </c>
       <c r="C187">
-        <v>-0.8379266278928105</v>
+        <v>0.1224559170967502</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>1.011622683394284</v>
+        <v>-0.9344022910710306</v>
       </c>
       <c r="C188">
-        <v>-0.1263346072872555</v>
+        <v>0.7455940882150568</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>-0.697293185883241</v>
+        <v>0.2799129580844549</v>
       </c>
       <c r="C189">
-        <v>2.038065227323758</v>
+        <v>-1.153624787899342</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>0.6013736486805671</v>
+        <v>-2.855180105784163</v>
       </c>
       <c r="C190">
-        <v>-0.1255513016908362</v>
+        <v>-0.4283097921571331</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>-0.4098876325361761</v>
+        <v>0.5841677402580329</v>
       </c>
       <c r="C191">
-        <v>-0.7685635891338748</v>
+        <v>1.013521027492346</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>-0.5411287282468356</v>
+        <v>-0.2842997483566879</v>
       </c>
       <c r="C192">
-        <v>0.1002450573259231</v>
+        <v>-0.2537758077327473</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>1.103120650479078</v>
+        <v>-0.2391352501710116</v>
       </c>
       <c r="C193">
-        <v>-1.327242898763096</v>
+        <v>-0.5953992196878003</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>-0.4646569474739355</v>
+        <v>-1.18574080698961</v>
       </c>
       <c r="C194">
-        <v>-1.621177397797997</v>
+        <v>-0.7213257127461168</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.9876782057069545</v>
+        <v>0.8478198524223606</v>
       </c>
       <c r="C195">
-        <v>-0.8820232411581578</v>
+        <v>0.8533507113489566</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>0.8612752545078763</v>
+        <v>1.017997803058402</v>
       </c>
       <c r="C196">
-        <v>0.1380936340796902</v>
+        <v>0.5130616132057912</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>-0.9940599280524436</v>
+        <v>-1.048635700909434</v>
       </c>
       <c r="C197">
-        <v>1.297352532486078</v>
+        <v>-2.033198557805556</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>-0.03885574490791872</v>
+        <v>0.5733650060322958</v>
       </c>
       <c r="C198">
-        <v>0.1190599331061429</v>
+        <v>-0.2122994703558835</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>-0.2041534397437298</v>
+        <v>0.6768977418925557</v>
       </c>
       <c r="C199">
-        <v>-0.2408370693202487</v>
+        <v>-0.9992837398570316</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>1.111173959714626</v>
+        <v>0.5343111634759935</v>
       </c>
       <c r="C200">
-        <v>-0.8016024130249302</v>
+        <v>1.150740494110837</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>1.067439110405364</v>
+        <v>-0.3841826008316642</v>
       </c>
       <c r="C201">
-        <v>0.0667749378254332</v>
+        <v>-0.1856855666994277</v>
       </c>
     </row>
   </sheetData>
